--- a/examples/templates/production-showcase-template.xlsx
+++ b/examples/templates/production-showcase-template.xlsx
@@ -8,14 +8,16 @@
     <sheet sheetId="2" name="Students" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Loops" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Matrix" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Contracts" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="DynamicHeader" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="DepartmentReport" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Contracts" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
   <si>
     <t>Excel Template Engine - Production Showcase</t>
   </si>
@@ -129,6 +131,51 @@
   </si>
   <si>
     <t>{{#grid students subjects}}{{score}}{{/grid}}</t>
+  </si>
+  <si>
+    <t>Dynamic Grouped Header Test</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>{{#each-col groups span=size reserve=8}}{{name}}{{/each-col}}</t>
+  </si>
+  <si>
+    <t>{{#each-col groupCols reserve=8}}{{col}}{{/each-col}}</t>
+  </si>
+  <si>
+    <t>{{#block rows}}</t>
+  </si>
+  <si>
+    <t>{{label}}</t>
+  </si>
+  <si>
+    <t>{{#each-col rowCols reserve=8}}{{value}}{{/each-col}}</t>
+  </si>
+  <si>
+    <t>Department Overtime Report</t>
+  </si>
+  <si>
+    <t>Lecturer</t>
+  </si>
+  <si>
+    <t>{{#each-col semesterGroups span=colCount reserve=8}}{{name}}{{/each-col}}</t>
+  </si>
+  <si>
+    <t>{{#each-col semesterColumns reserve=8}}{{name}}{{/each-col}}</t>
+  </si>
+  <si>
+    <t>{{#block departments}}</t>
+  </si>
+  <si>
+    <t>{{index}}. {{name}}</t>
+  </si>
+  <si>
+    <t>{{#block lecturers}}</t>
+  </si>
+  <si>
+    <t>{{#each-col values reserve=8}}{{value}}{{/each-col}}</t>
   </si>
   <si>
     <t>Contracts - Block Clone</t>
@@ -831,6 +878,169 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="9" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+      <c r="B3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="10" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A5:J5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -840,7 +1050,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -848,12 +1058,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
@@ -861,21 +1071,21 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3">
         <f>D4*2</f>
@@ -885,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
